--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -67,14 +67,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCEEFF"/>
-        <bgColor rgb="00DCEEFF"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,10 +112,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,36 +495,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Workstream</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>What Damco Handles</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>What Damco Does</t>
+          <t>What We Need From You</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>What We Need From Will</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -526,393 +531,305 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="35" customHeight="1">
+    </row>
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>On-Page SEO</t>
+          <t>Blog — July post 1
+"Why Professional School Photography Matters"</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Blog Writing</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Damco writes the blog post and shares for review</t>
+          <t>Written and ready to publish</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Senthil to upload to website</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Review and approve the draft before publishing</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on Senthil</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Blog — July post 2
+"Why School Photography Matters / What to Look for in a New Photographer"</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Writing in progress</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Review draft when shared, then approve</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>22 July 2026</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2 per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="35" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>On-Page SEO</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Blog Publishing</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Will's team (Senthil) uploads approved blog to website</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Senthil to upload once Will approves</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Blog — "How to Choose a School Photography Company in the UK"</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Published on website — SEO audit done, fixes sent to Senthil</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Will to send corrected blog content</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Waiting on Will</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>FAQs</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Written and ready — schema code prepared for Senthil</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Will to complete review and approve</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Waiting on Will</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Website Fixes
+(Forms, CAPTCHA, Thank You pages)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Specifications sent to Senthil with full detail</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Senthil to implement and confirm live date</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on Senthil</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Quora</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Damco writes all answers — nothing for your team to write</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Review draft answers before we post — quick read and approve</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Ongoing — weekly</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2 per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>On-Page SEO</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>FAQ Writing</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Damco writes FAQ answers and shares for review</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Review and approve answers before going live</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Done — pending publish</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>One-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>On-Page SEO</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SEO Audit</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Damco audits published pages and sends fixes to Senthil</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>No action needed — Senthil handles fixes</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Damco writes all answers — nothing for your team to write</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Confirm the 3 questions shared are relevant topics for Imago</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8 July 2026</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Waiting on Will</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Third-Party Articles</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Damco writes all articles and manages the account</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Review each article draft before we publish — approve or request changes</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SEO Audit — Blog Pages</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Damco audits all published blogs and sends fixes to Senthil</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>No action needed from Will's side</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>On-Page SEO</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Schema / Structured Data</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Damco prepares schema code and sends to Senthil</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No action needed — Senthil adds the code</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Per page</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Technical SEO</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Website Fixes</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Damco identifies issues and shares with Senthil</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>No action needed — Senthil implements</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Monthly SEO Dashboard</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Damco prepares and shares every month</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Review the report — flag any questions</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>End of each month</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LLM Visibility
+(ChatGPT, Perplexity, Google AI)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Damco monitors and builds citations across platforms</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>No action needed from Will's side</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Monthly check — 31 July 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="35" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Off-Page SEO</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Quora</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Damco writes answers and shares drafts for approval</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Review and approve before posting</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="35" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Off-Page SEO</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Damco identifies questions and writes answers</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Review and confirm topics are relevant</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Pending Approval</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="35" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Off-Page SEO</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Third-Party Articles</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Damco writes articles and shares for approval</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Review and approve before anything goes live</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="35" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Off-Page SEO</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Business Directories</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Damco submits Imago to relevant directories</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>No action needed</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>One-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="35" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>AEO / GEO</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>LLM Visibility (ChatGPT / Perplexity)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Damco monitors and builds citations across platforms</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>No action needed</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Monthly check</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="35" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Reporting</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Monthly SEO Dashboard</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Damco prepares and shares monthly report</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Review the dashboard</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Monthly</t>
         </is>
       </c>
     </row>

--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -834,6 +834,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid status" promptTitle="Status" prompt="Select a status" type="list">
+      <formula1>"In Progress,Waiting on Will,Waiting on Senthil,Done,Live,Planned"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="SEO Activity Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="22 Jul 2026 — Call Agenda" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +34,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00842029"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00664D03"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00155724"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +122,26 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -104,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -129,6 +194,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -715,7 +807,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>22 July 2026</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -841,4 +933,295 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Call Agenda — Imago Photography  |  22 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Discussion Points</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>What We Need / Outcome</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="53" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>One-Pager Walkthrough</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>• Walk Will through each workstream — On-Page, Technical, Off-Page, AEO/GEO
+• Clarify what Damco handles vs what requires Will or Senthil
+• Confirm Will is comfortable with the approval process for Quora, Reddit, Medium</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Will confirms he has a clear picture of all activities and what his team needs to do</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Blog Update</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>• Blog 1 ("Why Professional School Photography Matters") — is it live yet? If not, get Senthil's timeline
+• Blog 2 ("Why School Photography Matters") — share writing update, confirm Will is reviewing</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Confirm live date for Blog 1. Get Will's approval on Blog 2 draft</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Ashish / Senthil</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="83" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Reddit Approval</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>• 3 questions shared — still pending Will's sign-off
+• r/photography — school photography discussion
+• r/Nikon — share Imago's images as brand expression
+• r/UKParenting — UK parents discussing school photo packages
+• Reminder: Damco writes everything, no time needed from Will's team</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Yes or no on each question — approval to post</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="53" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SEO Audit Fixes</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>• Fixes sent to Senthil on 8 July — headings, internal links, meta title/description, alt text, schema
+• Without these fixes the blog will struggle to rank regardless of content quality
+• Confirm Senthil received the email and understands each fix</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Agree a deadline for all fixes to go live</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Senthil</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="68" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Medium / Third-Party Content</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>• Medium account live: medium.com/@MarketingSupport_61400
+• Confirm Will has the login details
+• Share first article draft for review if ready
+• Vocal.media is next platform after Medium — flag this</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Will confirms receipt of login. Approve or request changes on first draft</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Ashish / Will</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>August Blog Topics</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>• Recommend back-to-school angle — positions Imago for September search traffic
+• Suggest 2 topics for Will to approve today so writing can begin
+• Reminder: topics must be approved before writing starts</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Will approves 2 blog topics for August</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Ashish / Will</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="53" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Quora Update</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>• 2 answers posted this month — "How are large schools photographed?" and "How can parents prepare kids?"
+• Cadence: 1 per week, Damco shares draft before posting
+• Confirm Will is happy with the approval process</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Will confirms the process is working</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Actions Lock</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>• Agree all outstanding actions — owner and deadline for each
+• Key pending items: Blog 1 live date (Senthil), Reddit approval (Will), Blog 2 review (Will), SEO fixes deadline (Senthil)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Every open action has a named owner and a date</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1218,6 +1218,65 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="53" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>GTM Implementation</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>• Google Tag Manager setup has been assigned to Senthil
+• Confirm Senthil has received the GTM requirements and access
+• Agree a go-live deadline for GTM to be implemented on the website</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Senthil confirms receipt and provides a live date for GTM implementation</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Senthil</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Web Page Content — Audit &amp; Pending Updates</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>• Damco shared content suggestions for multiple web pages
+• Following the audit, changes have been made on the School Photography page only
+• All remaining pages are still pending — content updates not yet applied
+• Agree which pages to prioritise next and set a timeline with Senthil</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Confirm remaining pages are on Senthil's list. Agree priority order and deadline for next batch of content updates</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Senthil / Ashish</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>

--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -4,8 +4,6 @@
   <workbookPr/>
   <sheets>
     <sheet name="SEO Activity Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="22 Jul 2026 — Call Agenda" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SEO Audit — Priority Fixes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28909,567 +28907,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" style="28" min="1" max="1"/>
-    <col width="44" customWidth="1" style="28" min="2" max="2"/>
-    <col width="36" customWidth="1" style="28" min="3" max="3"/>
-    <col width="16" customWidth="1" style="28" min="4" max="4"/>
-    <col width="14" customWidth="1" style="28" min="5" max="5"/>
-    <col width="16" customWidth="1" style="28" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" s="28">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>Call Agenda — Imago Photography  |  22 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="28">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="B2" s="30" t="inlineStr">
-        <is>
-          <t>Discussion Points</t>
-        </is>
-      </c>
-      <c r="C2" s="30" t="inlineStr">
-        <is>
-          <t>What We Need / Outcome</t>
-        </is>
-      </c>
-      <c r="D2" s="30" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="E2" s="30" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F2" s="30" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="53" customHeight="1" s="28">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>Blog SEO — On-Page</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>• Blog 1 ("Why Professional School Photography Matters") — Will has shared both blogs for review
-• Blog 2 ("Why School Photography Matters") — review draft received
-• Confirm Senthil's live date for Blog 1 on website</t>
-        </is>
-      </c>
-      <c r="C3" s="33" t="inlineStr">
-        <is>
-          <t>Confirm live date for Blog 1. Get Will's approval on Blog 2 draft</t>
-        </is>
-      </c>
-      <c r="D3" s="34" t="inlineStr">
-        <is>
-          <t>Ashish</t>
-        </is>
-      </c>
-      <c r="E3" s="35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" s="34" t="inlineStr">
-        <is>
-          <t>24 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="83" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Reddit Approval</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>• 3 questions shared — still pending Will's sign-off
-• r/photography — school photography discussion
-• r/Nikon — share Imago's images as brand expression
-• r/UKParenting — UK parents discussing school photo packages
-• Reminder: Damco writes everything, no time from Will's team needed</t>
-        </is>
-      </c>
-      <c r="C4" s="33" t="inlineStr">
-        <is>
-          <t>Yes or no on each question — approval to post</t>
-        </is>
-      </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>Will</t>
-        </is>
-      </c>
-      <c r="E4" s="35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="inlineStr">
-        <is>
-          <t>29 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="53" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>SEO Audit Fixes</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>• Fixes sent to Senthil on 8 July — headings, internal links, meta title/description, alt text, schema
-• Without these fixes the blog will not rank regardless of content quality
-• Fixes have been ranked by impact (see SEO Audit Priority sheet)</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>Agree a deadline for all fixes to go live</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-      <c r="E5" s="35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>29 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="68" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>Web Page Content — Pending Updates</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>• Damco shared content suggestions for multiple web pages
-• School Photography page — changes applied after audit
-• All remaining pages still pending — content updates not yet applied
-• Agree which pages to prioritise next</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>Confirm remaining pages are on Senthil's list. Agree priority order and deadline for next batch</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>Senthil / Ashish</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F6" s="34" t="inlineStr">
-        <is>
-          <t>29 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="53" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>August Blog Topics</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>• Recommend back-to-school angle — positions Imago for September search traffic
-• Suggest 2 topics for Will to approve today so writing can begin
-• Topics must be approved before writing starts</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>Will approves 2 blog topics for August</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>Ashish / Will</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>29 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="53" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>GTM Implementation</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>• GTM setup assigned to Senthil
-• Thank You page part to be revised as part of this
-• Confirm Senthil has received requirements and access</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t>Senthil confirms live date for GTM implementation</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>29 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="53" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>Quora Update</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>• 2 answers posted this month — "How are large schools photographed?" and "How can parents prepare kids?"
-• Cadence: 1 per week — Damco shares draft before posting
-• Will to share Quora drafts for review today</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>Will confirms approval process is working</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>Ashish</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" style="28" min="1" max="1"/>
-    <col width="44" customWidth="1" style="28" min="2" max="2"/>
-    <col width="20" customWidth="1" style="28" min="3" max="3"/>
-    <col width="20" customWidth="1" style="28" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" s="28">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>SEO Audit — Blog Fixes Ranked by Impact  |  How to Choose a School Photography Company</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="28">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Fixes are ranked in order of SEO impact. Start with Critical — these have the highest effect on rankings. Do Important next. Good to have can wait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" s="28">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>Fix Required</t>
-        </is>
-      </c>
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>Why It Matters</t>
-        </is>
-      </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>Impact Level</t>
-        </is>
-      </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" s="28">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>3 H1 tags on the page (should be 1 only)</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Multiple H1s split ranking signals — search engines cannot determine the primary topic of the page</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>Critical — do first</t>
-        </is>
-      </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" s="28">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>Article title coded as H3 instead of H2</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Heading hierarchy must flow H1 → H2 → H3. Incorrect structure reduces how well search engines read the content</t>
-        </is>
-      </c>
-      <c r="C5" s="35" t="inlineStr">
-        <is>
-          <t>Critical — do first</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>All section headings are H3 — no H2 used</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>Page jumps from H1 straight to H3 with no H2, breaking content structure for search engines</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="inlineStr">
-        <is>
-          <t>Critical — do first</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" s="28">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>No Article schema on the page</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Schema helps search engines understand the content type and can improve how the page appears in results</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>Critical — do first</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" s="28">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>Only 1 internal link — 10 more identified</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Internal links help search engines discover other pages and pass authority across the site</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>Important — do next</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" s="28">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>Title tag is 74 characters (max 60)</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>Titles over 60 characters are cut off in search results, reducing click-through rates</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>Important — do next</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" s="28">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>Meta description is 122 characters (min 150–160)</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>Short descriptions reduce click-through rates — search engines may auto-generate a less relevant snippet</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>Important — do next</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="28">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>2 images missing alt text</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Alt text helps search engines understand images and is required for accessibility compliance</t>
-        </is>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
-        <is>
-          <t>Good to have — when ready</t>
-        </is>
-      </c>
-      <c r="D11" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" s="28">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>No outbound links to credible sources</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>Authoritative content is expected to reference credible sources, particularly on trust-sensitive topics like safeguarding</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>Good to have — when ready</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>Senthil</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -254,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -366,6 +366,18 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,22 +721,22 @@
 "Why Professional School Photography Matters"</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
-          <t>Written and ready to publish</t>
+          <t>Written and ready to publish — Will has shared blog content for review</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="40" t="inlineStr">
         <is>
-          <t>Senthil to upload to website</t>
+          <t>Senthil to upload to website once reviewed</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="40" t="inlineStr">
         <is>
-          <t>ASAP — discussed 22 Jul</t>
+          <t>25 July 2026</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="41" t="inlineStr">
         <is>
           <t>Waiting on Senthil</t>
         </is>
@@ -758,24 +770,24 @@
 "Why School Photography Matters / What to Look for in a New Photographer"</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>Writing in progress</t>
+          <t>Writing in progress — draft to be shared with Will for approval</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
-          <t>Review draft when shared, then approve</t>
+          <t>Review and approve draft when shared</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
-          <t>24 July 2026</t>
+          <t>25 July 2026</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
-          <t>Waiting on Will</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F3" s="13" t="n"/>
@@ -806,24 +818,24 @@
           <t>Blog — "How to Choose a School Photography Company in the UK"</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
-          <t>Published on website — SEO audit done, fixes sent to Senthil</t>
+          <t>Published on website — SEO audit done, fixes sent to Senthil on 8 July</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
-          <t>Will to send corrected blog content</t>
+          <t>No action needed from Will — Senthil to implement fixes</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
-          <t>ASAP</t>
+          <t>29 July 2026</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>Waiting on Will</t>
+          <t>Waiting on Senthil</t>
         </is>
       </c>
       <c r="F4" s="13" t="n"/>
@@ -854,22 +866,22 @@
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Written and ready — schema code prepared for Senthil</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Will to complete review and approve</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>ASAP</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>Waiting on Will</t>
         </is>
@@ -903,22 +915,22 @@
 (Forms, CAPTCHA, Thank You pages)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>Specifications sent to Senthil with full detail</t>
+          <t>Specifications sent to Senthil — GTM and Thank You page part to be revised</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Senthil to implement and confirm live date</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>ASAP</t>
+          <t>29 July 2026</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>Waiting on Senthil</t>
         </is>
@@ -951,22 +963,22 @@
           <t>Quora</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
-          <t>Damco writes all answers — nothing for your team to write</t>
+          <t>Damco writes all answers — drafts shared with Will before posting</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
-          <t>Review draft answers before we post — quick read and approve</t>
+          <t>Review and approve draft answers — quick read and approve</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Ongoing — weekly</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -999,22 +1011,22 @@
           <t>Reddit</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>Damco writes all answers — nothing for your team to write</t>
+          <t>Damco writes all answers — 3 questions shared with Will for topic approval</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>Confirm the 3 questions shared are relevant topics for Imago</t>
+          <t>Confirm the 3 questions are relevant — yes or no on each</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>29 July 2026</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="43" t="inlineStr">
         <is>
           <t>Waiting on Will</t>
         </is>
@@ -1047,22 +1059,22 @@
           <t>Medium / Third-Party Articles</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>Damco writes all articles and manages the account</t>
+          <t>Damco writes all articles — Medium account live, first draft being prepared</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>Review each article draft before we publish — approve or request changes</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="41" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -1095,22 +1107,22 @@
           <t>SEO Audit — Blog Pages</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>Damco audits all published blogs and sends fixes to Senthil</t>
+          <t>Audits done — fixes sent to Senthil. Fixes ranked by priority (Critical / Important / Good to have)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
-          <t>No action needed from Will's side</t>
+          <t>No action needed from Will — Senthil implements fixes</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="40" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -1143,22 +1155,22 @@
           <t>Monthly SEO Dashboard</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
-          <t>Damco prepares and shares every month</t>
+          <t>Damco prepares and shares monthly — due 20th of each month</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>Review the report — flag any questions</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>End of each month</t>
+          <t>20 August 2026</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="41" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -1192,22 +1204,22 @@
 (ChatGPT, Perplexity, Google AI)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>Damco monitors and builds citations across platforms</t>
+          <t>Damco monitors Imago visibility in ChatGPT, Perplexity, and Google AI Overviews</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>No action needed from Will's side</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
-          <t>Monthly check — 31 July 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="41" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>

--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -820,22 +820,22 @@
       </c>
       <c r="B4" s="40" t="inlineStr">
         <is>
-          <t>Published on website — SEO audit done, fixes sent to Senthil on 8 July</t>
+          <t>Published on website — SEO audit done; fixes sent to Senthil on 8 July</t>
         </is>
       </c>
       <c r="C4" s="40" t="inlineStr">
         <is>
-          <t>No action needed from Will — Senthil to implement fixes</t>
+          <t>Will to send corrected blog content</t>
         </is>
       </c>
       <c r="D4" s="40" t="inlineStr">
         <is>
-          <t>29 July 2026</t>
+          <t>ASAP</t>
         </is>
       </c>
       <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>Waiting on Senthil</t>
+          <t>Waiting on Will</t>
         </is>
       </c>
       <c r="F4" s="13" t="n"/>
@@ -912,12 +912,12 @@
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Website Fixes
-(Forms, CAPTCHA, Thank You pages)</t>
+(Forms, CAPTCHA, Thank You pages, GTM)</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>Specifications sent to Senthil — GTM and Thank You page part to be revised</t>
+          <t>Specifications sent to Senthil — GTM and Thank You page implementation included</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>Audits done — fixes sent to Senthil. Fixes ranked by priority (Critical / Important / Good to have)</t>
+          <t>Audits done — fixes ranked by priority (Critical / Important / Good to have) and sent to Senthil</t>
         </is>
       </c>
       <c r="C10" s="40" t="inlineStr">

--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -143,8 +143,18 @@
       <color rgb="00595959"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -219,8 +229,43 @@
         <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F39C12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0095A5A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F3F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A252F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -250,11 +295,43 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -377,6 +454,38 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -657,37 +766,37 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="97.56999999999999" customWidth="1" style="28" min="1" max="1"/>
-    <col width="76" customWidth="1" style="28" min="2" max="2"/>
-    <col width="94.86" customWidth="1" style="28" min="3" max="3"/>
-    <col width="38.86" customWidth="1" style="28" min="4" max="4"/>
-    <col width="27.14" customWidth="1" style="28" min="5" max="5"/>
+    <col width="35" customWidth="1" style="28" min="1" max="1"/>
+    <col width="40" customWidth="1" style="28" min="2" max="2"/>
+    <col width="35" customWidth="1" style="28" min="3" max="3"/>
+    <col width="22" customWidth="1" style="28" min="4" max="4"/>
+    <col width="20" customWidth="1" style="28" min="5" max="5"/>
     <col width="8.859999999999999" customWidth="1" style="28" min="6" max="6"/>
     <col width="8.710000000000001" customWidth="1" style="28" min="7" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="28">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="28">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="44" t="inlineStr">
         <is>
           <t>What Damco Handles</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="44" t="inlineStr">
         <is>
           <t>What We Need From You</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="44" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="44" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -715,32 +824,15 @@
       <c r="Z1" s="2" t="n"/>
     </row>
     <row r="2" ht="14.25" customHeight="1" s="28">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
-          <t>Blog — July post 1
-"Why Professional School Photography Matters"</t>
+          <t>ACTIVE — Damco actioning now</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
-        <is>
-          <t>Written and ready to publish — Will has shared blog content for review</t>
-        </is>
-      </c>
-      <c r="C2" s="40" t="inlineStr">
-        <is>
-          <t>Senthil to upload to website once reviewed</t>
-        </is>
-      </c>
-      <c r="D2" s="40" t="inlineStr">
-        <is>
-          <t>25 July 2026</t>
-        </is>
-      </c>
-      <c r="E2" s="41" t="inlineStr">
-        <is>
-          <t>Waiting on Senthil</t>
-        </is>
-      </c>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="47" t="n"/>
       <c r="F2" s="13" t="n"/>
       <c r="G2" s="13" t="n"/>
       <c r="H2" s="13" t="n"/>
@@ -763,29 +855,29 @@
       <c r="Y2" s="13" t="n"/>
       <c r="Z2" s="13" t="n"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="28">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="50" customHeight="1" s="28">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>Blog — July post 2
 "Why School Photography Matters / What to Look for in a New Photographer"</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>Writing in progress — draft to be shared with Will for approval</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>Review and approve draft when shared</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>25 July 2026</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -812,30 +904,30 @@
       <c r="Y3" s="13" t="n"/>
       <c r="Z3" s="13" t="n"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="28">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="50" customHeight="1" s="28">
+      <c r="A4" s="48" t="inlineStr">
         <is>
-          <t>Blog — "How to Choose a School Photography Company in the UK"</t>
+          <t>Quora</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
-          <t>Published on website — SEO audit done; fixes sent to Senthil on 8 July</t>
+          <t>Damco writes all answers — drafts shared with Will before posting</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
-          <t>Will to send corrected blog content</t>
+          <t>Review and approve draft answers — quick read and approve</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
-          <t>ASAP</t>
+          <t>Ongoing — weekly</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
-          <t>Waiting on Will</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F4" s="13" t="n"/>
@@ -860,28 +952,28 @@
       <c r="Y4" s="13" t="n"/>
       <c r="Z4" s="13" t="n"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="28">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="50" customHeight="1" s="28">
+      <c r="A5" s="48" t="inlineStr">
         <is>
-          <t>FAQs</t>
+          <t>Reddit</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
-          <t>Written and ready — schema code prepared for Senthil</t>
+          <t>Damco writes all answers — 3 questions shared with Will for topic approval</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
-          <t>Will to complete review and approve</t>
+          <t>Confirm the 3 questions are relevant — yes or no on each</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
-          <t>ASAP</t>
+          <t>29 July 2026</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>Waiting on Will</t>
         </is>
@@ -908,31 +1000,30 @@
       <c r="Y5" s="13" t="n"/>
       <c r="Z5" s="13" t="n"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1" s="28">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="50" customHeight="1" s="28">
+      <c r="A6" s="48" t="inlineStr">
         <is>
-          <t>Website Fixes
-(Forms, CAPTCHA, Thank You pages, GTM)</t>
+          <t>Medium / Third-Party Articles</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
-          <t>Specifications sent to Senthil — GTM and Thank You page implementation included</t>
+          <t>Damco writes all articles — Medium account live, first draft being prepared</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
-          <t>Senthil to implement and confirm live date</t>
+          <t>Review each article draft before we publish — approve or request changes</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
-          <t>29 July 2026</t>
+          <t>Ongoing</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
-          <t>Waiting on Senthil</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F6" s="13" t="n"/>
@@ -957,28 +1048,28 @@
       <c r="Y6" s="13" t="n"/>
       <c r="Z6" s="13" t="n"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1" s="28">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="50" customHeight="1" s="28">
+      <c r="A7" s="48" t="inlineStr">
         <is>
-          <t>Quora</t>
+          <t>SEO Audit — Blog Pages</t>
         </is>
       </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
-          <t>Damco writes all answers — drafts shared with Will before posting</t>
+          <t>Audits done — fixes ranked by priority (Critical / Important / Good to have) and sent to Senthil</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
-          <t>Review and approve draft answers — quick read and approve</t>
+          <t>No action needed from Will — Senthil implements fixes</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
-          <t>Ongoing — weekly</t>
+          <t>Ongoing</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -1005,30 +1096,30 @@
       <c r="Y7" s="13" t="n"/>
       <c r="Z7" s="13" t="n"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1" s="28">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="50" customHeight="1" s="28">
+      <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Monthly SEO Dashboard</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
-          <t>Damco writes all answers — 3 questions shared with Will for topic approval</t>
+          <t>Damco prepares and shares monthly — due 20th of each month</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
-          <t>Confirm the 3 questions are relevant — yes or no on each</t>
+          <t>Review the report — flag any questions</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
-          <t>29 July 2026</t>
+          <t>20 August 2026</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
-          <t>Waiting on Will</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
@@ -1053,28 +1144,29 @@
       <c r="Y8" s="13" t="n"/>
       <c r="Z8" s="13" t="n"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1" s="28">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="50" customHeight="1" s="28">
+      <c r="A9" s="48" t="inlineStr">
         <is>
-          <t>Medium / Third-Party Articles</t>
+          <t>LLM Visibility
+(ChatGPT, Perplexity, Google AI)</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
-          <t>Damco writes all articles — Medium account live, first draft being prepared</t>
+          <t>Damco monitors Imago visibility in ChatGPT, Perplexity, and Google AI Overviews</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
-          <t>Review each article draft before we publish — approve or request changes</t>
+          <t>No action needed from Will's side</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>31 July 2026</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
@@ -1102,31 +1194,15 @@
       <c r="Z9" s="13" t="n"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="28">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
-          <t>SEO Audit — Blog Pages</t>
+          <t>WAITING — Pending Will's input</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>Audits done — fixes ranked by priority (Critical / Important / Good to have) and sent to Senthil</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>No action needed from Will — Senthil implements fixes</t>
-        </is>
-      </c>
-      <c r="D10" s="40" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="E10" s="41" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="47" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13" t="n"/>
@@ -1149,30 +1225,31 @@
       <c r="Y10" s="13" t="n"/>
       <c r="Z10" s="13" t="n"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1" s="28">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="50" customHeight="1" s="28">
+      <c r="A11" s="51" t="inlineStr">
         <is>
-          <t>Monthly SEO Dashboard</t>
+          <t>Blog — July post 1
+"Why Professional School Photography Matters"</t>
         </is>
       </c>
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>Damco prepares and shares monthly — due 20th of each month</t>
+          <t>Written and ready to publish — Will has shared blog content for review</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>Review the report — flag any questions</t>
+          <t>Senthil to upload to website once reviewed</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>25 July 2026</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="52" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Waiting on Senthil</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
@@ -1197,31 +1274,30 @@
       <c r="Y11" s="13" t="n"/>
       <c r="Z11" s="13" t="n"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1" s="28">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12" ht="50" customHeight="1" s="28">
+      <c r="A12" s="51" t="inlineStr">
         <is>
-          <t>LLM Visibility
-(ChatGPT, Perplexity, Google AI)</t>
+          <t>Blog — "How to Choose a School Photography Company in the UK"</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>Damco monitors Imago visibility in ChatGPT, Perplexity, and Google AI Overviews</t>
+          <t>Published on website — SEO audit done; fixes sent to Senthil on 8 July</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>No action needed from Will's side</t>
+          <t>Will to send corrected blog content</t>
         </is>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>ASAP</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="52" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Waiting on Will</t>
         </is>
       </c>
       <c r="F12" s="13" t="n"/>
@@ -1246,12 +1322,32 @@
       <c r="Y12" s="13" t="n"/>
       <c r="Z12" s="13" t="n"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1" s="28">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="13" t="n"/>
+    <row r="13" ht="50" customHeight="1" s="28">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>FAQs</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Written and ready — schema code prepared for Senthil</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>Will to complete review and approve</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="inlineStr">
+        <is>
+          <t>Waiting on Will</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="n"/>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="13" t="n"/>
@@ -1275,11 +1371,15 @@
       <c r="Z13" s="13" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1" s="28">
-      <c r="A14" s="13" t="n"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>PARKED — Website / on-page work (low period only)</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
+      <c r="E14" s="47" t="n"/>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>
@@ -1302,12 +1402,34 @@
       <c r="Y14" s="13" t="n"/>
       <c r="Z14" s="13" t="n"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="28">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="13" t="n"/>
+    <row r="15" ht="50" customHeight="1" s="28">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>Website Fixes
+(Forms, CAPTCHA, Thank You pages, GTM)
+⚑ Parked — to be done last week of August</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Specifications sent to Senthil — GTM and Thank You page implementation included</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>Senthil to implement and confirm live date</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>Last week of August 2026</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="13" t="n"/>
       <c r="H15" s="13" t="n"/>
@@ -28911,6 +29033,11 @@
       <c r="Z1000" s="13" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A14:E14"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"In Progress,Waiting on Will,Waiting on Senthil,Done,Live,Planned,Damco Team,Imago team"</formula1>

--- a/research/seo-activity-one-pager.xlsx
+++ b/research/seo-activity-one-pager.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -50,7 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F9FA"/>
+        <fgColor rgb="00F5F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,11 +88,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,14 +462,14 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Activity</t>
@@ -493,26 +496,25 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="52" customHeight="1">
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blog — July post 2
-"Why School Photography Matters / What to Look for in a New Photographer"</t>
+          <t>Blog 2 — Why School Photography Matters</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Writing in progress — draft to be shared with Will for approval</t>
+          <t>Writing draft</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Review and approve draft when shared</t>
+          <t>Approve draft when shared</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>25 July 2026</t>
+          <t>25 Jul 2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -521,26 +523,25 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="52" customHeight="1">
+    <row r="3" ht="38" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Blog — July post 1
-"Why Professional School Photography Matters"</t>
+          <t>Blog 1 — Why Professional School Photography Matters</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Written and ready to publish — Will has shared blog content for review</t>
+          <t>Written — content received from Will</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Senthil to upload to website once reviewed</t>
+          <t>Senthil to upload</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>25 July 2026</t>
+          <t>25 Jul 2026</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -549,20 +550,20 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="38" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Blog — "How to Choose a School Photography Company in the UK"</t>
+          <t>Blog — How to Choose a School Photography Company</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Published on website — SEO audit done; fixes sent to Senthil on 8 July</t>
+          <t>Audit done, fixes sent to Senthil</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Will to send corrected blog content</t>
+          <t>Send corrected blog content</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -576,7 +577,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="38" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>FAQs</t>
@@ -584,12 +585,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Written and ready — schema code prepared for Senthil</t>
+          <t>Written, schema ready for Senthil</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Will to complete review and approve</t>
+          <t>Review and approve</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -603,7 +604,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="38" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Quora</t>
@@ -611,17 +612,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Damco writes all answers — drafts shared with Will before posting</t>
+          <t>Writing answers, sharing drafts before posting</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Review and approve draft answers — quick read and approve</t>
+          <t>Approve each draft</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ongoing — weekly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -630,7 +631,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="38" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Reddit</t>
@@ -638,17 +639,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Damco writes all answers — 3 questions shared with Will for topic approval</t>
+          <t>3 questions shared for approval</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Confirm the 3 questions are relevant — yes or no on each</t>
+          <t>Approve or reject each question</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>29 July 2026</t>
+          <t>29 Jul 2026</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -657,7 +658,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="38" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Medium / Third-Party Articles</t>
@@ -665,12 +666,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Damco writes all articles — Medium account live, first draft being prepared</t>
+          <t>Writing articles, Medium account live</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Review each article draft before we publish — approve or request changes</t>
+          <t>Approve each article before publish</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -684,7 +685,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="38" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>SEO Audit — Blog Pages</t>
@@ -692,12 +693,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Audits done — fixes ranked by priority (Critical / Important / Good to have) and sent to Senthil</t>
+          <t>Fixes ranked Critical / Important / Good to have</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>No action needed from Will — Senthil implements fixes</t>
+          <t>No action needed — Senthil implements</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -711,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Monthly SEO Dashboard</t>
@@ -719,17 +720,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Damco prepares and shares monthly — due 20th of each month</t>
+          <t>Prepared and shared by 20th each month</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Review the report — flag any questions</t>
+          <t>Review and flag questions</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20 August 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -738,26 +739,25 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LLM Visibility
-(ChatGPT, Perplexity, Google AI)</t>
+          <t>LLM Visibility (ChatGPT, Perplexity, Google AI)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Damco monitors Imago visibility in ChatGPT, Perplexity, and Google AI Overviews</t>
+          <t>Monthly monitoring</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>No action needed from Will's side</t>
+          <t>No action needed</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -766,26 +766,25 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Website Fixes
-(Forms, CAPTCHA, Thank You pages, GTM)</t>
+          <t>Website Fixes (Forms, CAPTCHA, Thank You, GTM)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Specifications sent to Senthil — GTM and Thank You page implementation included</t>
+          <t>Specs sent to Senthil</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Senthil to implement and confirm live date</t>
+          <t>Senthil to implement</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
